--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_405_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_405_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>42:17</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>60:40</t>
+          <t>30:38</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>7</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>28:44</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>43:18</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>19</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>55:05</t>
+          <t>25:01</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
         <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>70:48</t>
+          <t>30:46</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>38.4%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>04:24</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>49.1%</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>25:25</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>26:54</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>106</v>
       </c>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>4</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>53:53</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>26:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,22 +4604,22 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
         <v>6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>45:18</t>
+          <t>25:17</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>27:06</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>10</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>50:45</t>
+          <t>30:44</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>7</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>36:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>26.4%</t>
         </is>
       </c>
     </row>
@@ -5860,10 +5860,10 @@
         <v>24</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>42:09</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>52:15</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6451,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>4</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>50:28</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,22 +6564,22 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -6784,16 +6784,16 @@
         <v>134</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>40</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_405_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_405_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>7</v>
@@ -2315,7 +2315,7 @@
         <v>19</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>106</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>4</v>
@@ -4684,7 +4684,7 @@
         <v>6</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X40" t="n">
         <v>10</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X41" t="n">
         <v>7</v>
@@ -5860,10 +5860,10 @@
         <v>24</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6451,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
         <v>4</v>
@@ -6784,16 +6784,16 @@
         <v>134</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
         <v>40</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_405_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_405_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -851,20 +851,20 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>44.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,10 +1739,10 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Y30" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,58 +4304,58 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
         <v>4</v>
       </c>
-      <c r="Y35" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AA35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>5</v>
-      </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,10 +5284,10 @@
         <v>3</v>
       </c>
       <c r="X40" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>4</v>
       </c>
       <c r="X41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6460,14 +6460,14 @@
         <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6493,25 +6493,25 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK46" t="n">
         <v>3</v>
       </c>
-      <c r="AK46" t="n">
-        <v>4</v>
-      </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -6796,14 +6796,14 @@
         <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Y48" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK48" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
